--- a/main/ig/FRSectionAlertsLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionAlertsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRSectionAlertsLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionAlertsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRSectionAlertsLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionAlertsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRSectionAlertsLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionAlertsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,13 +100,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-alerts</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-alerts|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-points-de-vigilances-non-code</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-points-de-vigilances-non-code|0.1.0</t>
   </si>
   <si>
     <t>FRLMAlerts</t>
@@ -136,7 +136,7 @@
     <t>FRCDAPointsDeVigilancesNonCode.text</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-composition-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-composition-document|0.1.0</t>
   </si>
   <si>
     <t>FRCompositionDocument.section:sectionAlerts</t>

--- a/main/ig/FRSectionAlertsLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionAlertsLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="52">
   <si>
     <t>Property</t>
   </si>
@@ -37,6 +37,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>FRSectionAlertsLMCDAFHIR</t>
+  </si>
+  <si>
     <t>Title</t>
   </si>
   <si>
@@ -52,10 +55,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:45:34+00:00</t>
+    <t>2026-08-31T15:12:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,7 +106,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-alerts|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMAlerts|0.1.0</t>
   </si>
   <si>
     <t/>
@@ -115,46 +121,55 @@
     <t>equivalent</t>
   </si>
   <si>
+    <t>Section</t>
+  </si>
+  <si>
     <t>FRCDAPointsDeVigilancesNonCode</t>
   </si>
   <si>
     <t>FRLMAlerts.codeSection</t>
   </si>
   <si>
-    <t>FRCDAPointsDeVigilancesNonCode.code</t>
+    <t>Section.code</t>
   </si>
   <si>
     <t>FRLMAlerts.titleSection</t>
   </si>
   <si>
-    <t>FRCDAPointsDeVigilancesNonCode.title</t>
+    <t>Section.title</t>
   </si>
   <si>
     <t>FRLMAlerts.description</t>
   </si>
   <si>
-    <t>FRCDAPointsDeVigilancesNonCode.text</t>
+    <t>Section.text</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-composition-document|0.1.0</t>
   </si>
   <si>
+    <t>Composition.section</t>
+  </si>
+  <si>
     <t>FRCompositionDocument.section:sectionAlerts</t>
   </si>
   <si>
-    <t>FRCompositionDocument.section:sectionAlerts.code</t>
-  </si>
-  <si>
-    <t>FRCompositionDocument.section:sectionAlerts.title</t>
-  </si>
-  <si>
-    <t>FRCompositionDocument.section:sectionAlerts.text</t>
+    <t>Composition.section.code</t>
+  </si>
+  <si>
+    <t>Composition.section.title</t>
+  </si>
+  <si>
+    <t>Composition.section.text</t>
   </si>
   <si>
     <t>FRLMAlerts.entry.alert</t>
   </si>
   <si>
-    <t>FRCompositionDocument.section:sectionAlerts.entry:Flag</t>
+    <t>Composition.section.entry</t>
+  </si>
+  <si>
+    <t>Flag</t>
   </si>
 </sst>
 </file>
@@ -323,79 +338,83 @@
       <c r="A4" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" t="s" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
@@ -411,87 +430,89 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>36</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -507,102 +528,106 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>45</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="E7" s="2"/>
+        <v>50</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>51</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/main/ig/FRSectionAlertsLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionAlertsLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:12:23+00:00</t>
+    <t>2026-09-04T14:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
